--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ15" headerRowCount="1">
-  <autoFilter ref="A1:CQ15"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR21" headerRowCount="1">
+  <autoFilter ref="A1:CR21"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$21)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$21)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ15"/>
+  <dimension ref="A1:CR21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1876,7 +1883,8 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
-      <c r="CQ2" s="24" t="inlineStr">
+      <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2169,7 +2177,8 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
-      <c r="CQ3" s="24" t="inlineStr">
+      <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2462,7 +2471,8 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
-      <c r="CQ4" s="24" t="inlineStr">
+      <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2755,7 +2765,8 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
-      <c r="CQ5" s="24" t="inlineStr">
+      <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3048,7 +3059,8 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
-      <c r="CQ6" s="24" t="inlineStr">
+      <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3341,7 +3353,8 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
-      <c r="CQ7" s="24" t="inlineStr">
+      <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3634,7 +3647,8 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
-      <c r="CQ8" s="24" t="inlineStr">
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3927,7 +3941,8 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4220,7 +4235,8 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4513,7 +4529,8 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4782,7 +4799,8 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5075,7 +5093,8 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5368,7 +5387,8 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5661,7 +5681,1628 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>9cfb866352784ae7</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:59.561456Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182202</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Maja Chwalinska</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.623502</v>
+      </c>
+      <c r="P16" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q16" s="28" t="n">
+        <v>0.194317</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4300 (aec-wta-majchw-talgib-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Talia Gibson</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Maja Chwalinska</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Maja Chwalinska</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Maja Chwalinska</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:35.666785Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>d661fb2c61054b14</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:59.561456Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T10:30Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>961-2026:182088</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Linda Klimovicova</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.578623</v>
+      </c>
+      <c r="P17" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q17" s="28" t="n">
+        <v>0.06881900000000001</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Elizara Yaneva p=0.421 vs Linda Klimovicova. Executable ask 0.5100 (aec-wta-linkli-eliyan-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Elizara Yaneva</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Linda Klimovicova</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Linda Klimovicova</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Linda Klimovicova</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:31.464146Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>2e9c1a64618a475f</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:59.561456Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:30Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181813</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Liam Draxl</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.69073</v>
+      </c>
+      <c r="P18" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q18" s="28" t="n">
+        <v>0.110898</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5800 (aec-atp-danagu-liadra-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Liam Draxl</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Liam Draxl</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Liam Draxl</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Daniel Merida</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:50.946314Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2bf4910313614143</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:59.561456Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181810</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Jack Draper</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Terence Atmane</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.781578</v>
+      </c>
+      <c r="P19" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q19" s="28" t="n">
+        <v>0.111611</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>76</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Jack Draper p=0.782 vs Terence Atmane. Executable ask 0.6700 (aec-atp-teratm-jacdra-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Jack Draper</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Jack Draper</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Jack Draper</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Terence Atmane</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Terence Atmane</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Terence Atmane</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:54.448463Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>dc4485a7a108487a</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:59.561456Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181748</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.701855</v>
+      </c>
+      <c r="P20" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q20" s="28" t="n">
+        <v>0.072225</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6300 (aec-atp-fratia-marcil-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Frances Tiafoe</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:59.800144Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>50b69d278ca14ea0</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:59.561456Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:30Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181769</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.62292</v>
+      </c>
+      <c r="P21" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q21" s="28" t="n">
+        <v>0.132724</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4900 (aec-atp-lucdar-gabdia-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Gabriel Diallo</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:01.150443Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR21" headerRowCount="1">
-  <autoFilter ref="A1:CR21"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS21" headerRowCount="1">
+  <autoFilter ref="A1:CS21"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR21"/>
+  <dimension ref="A1:CS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1884,7 +1891,8 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
-      <c r="CR2" s="24" t="inlineStr">
+      <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2178,7 +2186,8 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
-      <c r="CR3" s="24" t="inlineStr">
+      <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2472,7 +2481,8 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
-      <c r="CR4" s="24" t="inlineStr">
+      <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2766,7 +2776,8 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
-      <c r="CR5" s="24" t="inlineStr">
+      <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3060,7 +3071,8 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
-      <c r="CR6" s="24" t="inlineStr">
+      <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3354,7 +3366,8 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
-      <c r="CR7" s="24" t="inlineStr">
+      <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3648,7 +3661,8 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
-      <c r="CR8" s="24" t="inlineStr">
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3942,7 +3956,8 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
-      <c r="CR9" s="24" t="inlineStr">
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4236,7 +4251,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4530,7 +4546,8 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
-      <c r="CR11" s="24" t="inlineStr">
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4800,7 +4817,8 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
-      <c r="CR12" s="24" t="inlineStr">
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5094,7 +5112,8 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
-      <c r="CR13" s="24" t="inlineStr">
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5388,7 +5407,8 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5682,7 +5702,8 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
-      <c r="CR15" s="24" t="inlineStr">
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5691,7 +5712,7 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>9cfb866352784ae7</t>
+          <t>d661fb2c61054b14</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
@@ -5701,12 +5722,12 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00Z</t>
+          <t>2026-08-04T10:30Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182202</t>
+          <t>961-2026:182088</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5716,12 +5737,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5741,28 +5762,28 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>133</v>
+        <v>-104</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>2.33</v>
+        <v>1.961538</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.509804</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.623502</v>
+        <v>0.578623</v>
       </c>
       <c r="P16" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q16" s="28" t="n">
-        <v>0.194317</v>
+        <v>0.06881900000000001</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5771,21 +5792,41 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="28" t="n"/>
-      <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="Z16" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA16" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB16" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC16" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:02:55.340280Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4300 (aec-wta-majchw-talgib-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Elizara Yaneva p=0.421 vs Linda Klimovicova. Executable ask 0.5100 (aec-wta-linkli-eliyan-2026-08-03).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5795,7 +5836,7 @@
       </c>
       <c r="AG16" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH16" s="24" t="n"/>
@@ -5826,32 +5867,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Linda Klimovicova</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5904,7 +5945,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:35.666785Z</t>
+          <t>2026-08-04T08:53:31.464146Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5914,19 +5955,23 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>133</v>
+        <v>-104</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>2.33</v>
+        <v>1.961538</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.509804</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
       <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
-      <c r="BR16" s="28" t="n"/>
+      <c r="BQ16" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR16" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
       <c r="BU16" s="25" t="n"/>
@@ -5952,7 +5997,8 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
-      <c r="CR16" s="24" t="inlineStr">
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5961,22 +6007,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>d661fb2c61054b14</t>
+          <t>8df4f78345b2416b</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T10:30Z</t>
+          <t>2026-08-04T18:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182088</t>
+          <t>421-2026:182202</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5986,12 +6032,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -6011,28 +6057,28 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.17</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.460829</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.578623</v>
+        <v>0.623502</v>
       </c>
       <c r="P17" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q17" s="28" t="n">
-        <v>0.06881900000000001</v>
+        <v>0.162673</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -6055,7 +6101,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Elizara Yaneva p=0.421 vs Linda Klimovicova. Executable ask 0.5100 (aec-wta-linkli-eliyan-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4600 (aec-wta-majchw-talgib-2026-08-04).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6096,32 +6142,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Elizara Yaneva</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Linda Klimovicova</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -6174,7 +6220,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:31.464146Z</t>
+          <t>2026-08-04T14:23:27.218479Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6184,13 +6230,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.17</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.460829</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -6222,7 +6268,8 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6231,12 +6278,12 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>2e9c1a64618a475f</t>
+          <t>34a95956e9564070</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6281,13 +6328,13 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.694444</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.590164</v>
       </c>
       <c r="O18" s="28" t="n">
         <v>0.69073</v>
@@ -6296,10 +6343,10 @@
         <v>0.05</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>0.110898</v>
+        <v>0.100566</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>2</v>
@@ -6325,7 +6372,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5800 (aec-atp-danagu-liadra-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5900 (aec-atp-danagu-liadra-2026-08-03).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6444,7 +6491,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:50.946314Z</t>
+          <t>2026-08-04T14:23:40.504586Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6454,13 +6501,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.694444</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.590164</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6492,7 +6539,8 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6501,12 +6549,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>2bf4910313614143</t>
+          <t>ca1db046253f492f</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6714,7 +6762,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:54.448463Z</t>
+          <t>2026-08-04T14:23:45.147148Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6762,7 +6810,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6771,12 +6820,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>dc4485a7a108487a</t>
+          <t>ad8183bf5b564dee</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6821,13 +6870,13 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O20" s="28" t="n">
         <v>0.701855</v>
@@ -6836,10 +6885,10 @@
         <v>0.05</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>0.072225</v>
+        <v>0.061567</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="S20" s="29" t="n">
         <v>2</v>
@@ -6865,7 +6914,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6300 (aec-atp-fratia-marcil-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6400 (aec-atp-fratia-marcil-2026-08-05).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6984,7 +7033,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:59.800144Z</t>
+          <t>2026-08-04T14:23:53.532342Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6994,13 +7043,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -7032,7 +7081,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -7041,12 +7091,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>50b69d278ca14ea0</t>
+          <t>e2274e5a21ab4fbc</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:59.561456Z</t>
+          <t>2026-08-04T14:25:17.456036Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7091,13 +7141,13 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.469484</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.62292</v>
@@ -7106,10 +7156,10 @@
         <v>0.05</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.132724</v>
+        <v>0.153436</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>1.5</v>
@@ -7135,7 +7185,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4900 (aec-atp-lucdar-gabdia-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4700 (aec-atp-lucdar-gabdia-2026-08-05).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7254,7 +7304,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:01.150443Z</t>
+          <t>2026-08-04T14:23:55.350978Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7264,13 +7314,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.469484</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7302,7 +7352,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS21" headerRowCount="1">
-  <autoFilter ref="A1:CS21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
+  <autoFilter ref="A1:CS29"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$21)</f>
+        <f>COUNTA('Picks'!$A$2:$A$29)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$21,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")/(COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"win")+COUNTIFS('Picks'!$BX$2:$BX$21,"&gt;0",'Picks'!$V$2:$V$21,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$21)/SUM('Picks'!$BX$2:$BX$21),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$21)</f>
+        <f>SUM('Picks'!$BY$2:$BY$29)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$21,"&lt;&gt;",'Picks'!$AB$2:$AB$21),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$21,'Picks'!$AM$2:$AM$21,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A14,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A15,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled",'Picks'!$V$2:$V$21,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$21,'Picks'!$H$2:$H$21,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$21,'Picks'!$H$2:$H$21,$A16,'Picks'!$U$2:$U$21,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS21"/>
+  <dimension ref="A1:CS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4636,18 +4636,38 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:39.165848Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Adrian Mannarino p=0.565 vs Jacob Fearnley. Executable ask 0.4000 (aec-atp-jacfea-adrman-2026-08-03).</t>
@@ -4660,7 +4680,7 @@
       </c>
       <c r="AG12" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH12" s="24" t="n"/>
@@ -4790,8 +4810,12 @@
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.4</v>
+      </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -6007,22 +6031,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>8df4f78345b2416b</t>
+          <t>15d8ba8c18cb4af9</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-04T15:02:48.664333Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00Z</t>
+          <t>2026-08-04T16:30Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182202</t>
+          <t>421-2026:181813</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -6032,12 +6056,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -6057,28 +6081,28 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>117</v>
+        <v>-144</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>2.17</v>
+        <v>1.694444</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.590164</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.623502</v>
+        <v>0.69073</v>
       </c>
       <c r="P17" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q17" s="28" t="n">
-        <v>0.162673</v>
+        <v>0.100566</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -6087,21 +6111,41 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:40.052341Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4600 (aec-wta-majchw-talgib-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5900 (aec-atp-danagu-liadra-2026-08-03).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6142,32 +6186,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Talia Gibson</t>
+          <t>Liam Draxl</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Maja Chwalinska</t>
+          <t>Daniel Merida</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -6220,7 +6264,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:27.218479Z</t>
+          <t>2026-08-04T15:01:10.821337Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6230,19 +6274,23 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>117</v>
+        <v>-144</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>2.17</v>
+        <v>1.694444</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.590164</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6278,22 +6326,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>34a95956e9564070</t>
+          <t>0932626ebe0641d3</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-04T16:52:13.548572Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30Z</t>
+          <t>2026-08-04T18:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181813</t>
+          <t>421-2026:182202</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6303,12 +6351,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6328,28 +6376,28 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-144</v>
+        <v>122</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.22</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.45045</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.69073</v>
+        <v>0.623502</v>
       </c>
       <c r="P18" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q18" s="28" t="n">
-        <v>0.100566</v>
+        <v>0.173052</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6358,21 +6406,41 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="28" t="n"/>
-      <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:40.245109Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Liam Draxl p=0.309 vs Daniel Merida. Executable ask 0.5900 (aec-atp-danagu-liadra-2026-08-03).</t>
+          <t>Surface-blended Elo on Hard: Talia Gibson p=0.376 vs Maja Chwalinska. Executable ask 0.4500 (aec-wta-majchw-talgib-2026-08-04).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6382,7 +6450,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6413,32 +6481,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Liam Draxl</t>
+          <t>Talia Gibson</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Daniel Merida</t>
+          <t>Maja Chwalinska</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6491,7 +6559,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:40.504586Z</t>
+          <t>2026-08-04T16:50:30.241150Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6501,19 +6569,23 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-144</v>
+        <v>122</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.22</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.45045</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
-      <c r="BR18" s="28" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
       <c r="BU18" s="25" t="n"/>
@@ -6549,12 +6621,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>ca1db046253f492f</t>
+          <t>59c5fd2e82144477</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-04T16:52:13.548572Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6629,18 +6701,38 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="28" t="n"/>
-      <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="Z19" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA19" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB19" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:58:40.439256Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Jack Draper p=0.782 vs Terence Atmane. Executable ask 0.6700 (aec-atp-teratm-jacdra-2026-08-03).</t>
@@ -6653,7 +6745,7 @@
       </c>
       <c r="AG19" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH19" s="24" t="n"/>
@@ -6762,7 +6854,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:45.147148Z</t>
+          <t>2026-08-04T16:50:46.373890Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6783,8 +6875,12 @@
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
-      <c r="BR19" s="28" t="n"/>
+      <c r="BQ19" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR19" s="28" t="n">
+        <v>0.67</v>
+      </c>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
       <c r="BU19" s="25" t="n"/>
@@ -6820,22 +6916,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>ad8183bf5b564dee</t>
+          <t>fa4f77bf385443e6</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-05T04:36:19.625619Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:00Z</t>
+          <t>2026-08-05T15:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181748</t>
+          <t>421-2026:182220</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6845,12 +6941,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6870,25 +6966,25 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-178</v>
+        <v>-285</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.350877</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.74026</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.701855</v>
+        <v>0.795002</v>
       </c>
       <c r="P20" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>0.061567</v>
+        <v>0.054742</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S20" s="29" t="n">
         <v>2</v>
@@ -6914,7 +7010,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Marin Cilic p=0.298 vs Frances Tiafoe. Executable ask 0.6400 (aec-atp-fratia-marcil-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Kayla Cross p=0.205 vs Ann Li. Executable ask 0.7400 (aec-wta-annli-kaycro-2026-08-04).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6955,32 +7051,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Marin Cilic</t>
+          <t>Kayla Cross</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Frances Tiafoe</t>
+          <t>Ann Li</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6998,7 +7094,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -7013,7 +7109,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -7028,12 +7124,12 @@
       </c>
       <c r="BG20" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:53.532342Z</t>
+          <t>2026-08-05T04:34:10.491214Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7043,13 +7139,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-178</v>
+        <v>-285</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.350877</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.74026</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -7091,22 +7187,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>e2274e5a21ab4fbc</t>
+          <t>f5c109203b344abd</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:17.456036Z</t>
+          <t>2026-08-05T04:36:19.625619Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:30Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181769</t>
+          <t>421-2026:182208</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -7116,12 +7212,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -7131,7 +7227,7 @@
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J21" s="25" t="n"/>
@@ -7141,28 +7237,28 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>113</v>
+        <v>-122</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2.13</v>
+        <v>1.819672</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.54955</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.62292</v>
+        <v>0.646211</v>
       </c>
       <c r="P21" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.153436</v>
+        <v>0.096661</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7185,7 +7281,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Gabriel Diallo p=0.377 vs Luciano Darderi. Executable ask 0.4700 (aec-atp-lucdar-gabdia-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5500 (aec-wta-alikor-emmnav-2026-08-04).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7226,32 +7322,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Gabriel Diallo</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Luciano Darderi</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7269,7 +7365,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7284,7 +7380,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7299,12 +7395,12 @@
       </c>
       <c r="BG21" s="24" t="inlineStr">
         <is>
-          <t>60749ecfb3f1405f12fbceda11b7e64f2473d40dd327256f9da20b2146b6ae03</t>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
         </is>
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:55.350978Z</t>
+          <t>2026-08-05T04:34:15.073339Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7314,13 +7410,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>113</v>
+        <v>-122</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>2.13</v>
+        <v>1.819672</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.54955</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7359,6 +7455,2174 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>aac54ca3098f486d</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:182214</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.733479</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q22" s="28" t="n">
+        <v>0.093191</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.6400 (aec-wta-liusam-barkre-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Barbora Krejcikova</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:19.786889Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>44bcccd381124b6e</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:30Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>961-2026:182098</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Mona Barthel</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Martyna Kubka</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="P23" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q23" s="28" t="n">
+        <v>0.194355</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Mona Barthel p=0.585 vs Martyna Kubka. Executable ask 0.3900 (aec-wta-markub-monbar-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Mona Barthel</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Mona Barthel</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Mona Barthel</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Martyna Kubka</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Martyna Kubka</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Martyna Kubka</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:10.279442Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>e020edf7cfeb46ad</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T12:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>961-2026:182097</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Veronika Podrez</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Susan Bandecchi</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.684504</v>
+      </c>
+      <c r="P24" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q24" s="28" t="n">
+        <v>0.165273</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5200 (aec-wta-susban-verpod-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Veronika Podrez</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Veronika Podrez</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Veronika Podrez</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Susan Bandecchi</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Susan Bandecchi</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Susan Bandecchi</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:10.339946Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>8e9660411beb46fe</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T15:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181727</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.629315</v>
+      </c>
+      <c r="P25" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q25" s="28" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Joao Fonseca p=0.629 vs Stefanos Tsitsipas. Executable ask 0.5700 (aec-atp-stetsi-joafon-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Joao Fonseca</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:29.605345Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>d2ae439197534b67</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:30Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181752</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.5960220000000001</v>
+      </c>
+      <c r="P26" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q26" s="28" t="n">
+        <v>0.096022</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.5000 (aec-atp-miokec-artrin-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Arthur Rinderknech</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:30.228623Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>f276d6d0260c4f9f</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T18:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181743</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.584869</v>
+      </c>
+      <c r="P27" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q27" s="28" t="n">
+        <v>0.184869</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4000 (aec-atp-hubhur-aletab-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:34.393571Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>21b78587ba4444b3</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181753</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.657899</v>
+      </c>
+      <c r="P28" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q28" s="28" t="n">
+        <v>0.257899</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Francisco Cerundolo p=0.658 vs Alex Michelsen. Executable ask 0.4000 (aec-atp-alemic-fracer-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Alex Michelsen</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:39.206890Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>8c4a1a66a49943db</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:19.625619Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181733</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.8122509999999999</v>
+      </c>
+      <c r="P29" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q29" s="28" t="n">
+        <v>0.082521</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Botic Van De Zandschulp p=0.188 vs Daniil Medvedev. Executable ask 0.7300 (aec-atp-danmed-botzan-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:42.085885Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS29" headerRowCount="1">
-  <autoFilter ref="A1:CS29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS30" headerRowCount="1">
+  <autoFilter ref="A1:CS30"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$29)</f>
+        <f>COUNTA('Picks'!$A$2:$A$30)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$30,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$30,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")/(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$30)/SUM('Picks'!$BX$2:$BX$30),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$29)</f>
+        <f>SUM('Picks'!$BY$2:$BY$30)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$30,"&lt;&gt;",'Picks'!$AB$2:$AB$30),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$30,'Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS29"/>
+  <dimension ref="A1:CS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6916,22 +6916,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>fa4f77bf385443e6</t>
+          <t>ebdce4914c024acf</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:21:33.669433Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T15:00Z</t>
+          <t>2026-08-05T10:30Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182220</t>
+          <t>961-2026:182098</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6966,28 +6966,28 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-285</v>
+        <v>156</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.350877</v>
+        <v>2.56</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.390625</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.795002</v>
+        <v>0.5849800000000001</v>
       </c>
       <c r="P20" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>0.054742</v>
+        <v>0.194355</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6996,21 +6996,41 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="28" t="n"/>
-      <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="Z20" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA20" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:49:58.226429Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Kayla Cross p=0.205 vs Ann Li. Executable ask 0.7400 (aec-wta-annli-kaycro-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Mona Barthel p=0.585 vs Martyna Kubka. Executable ask 0.3900 (aec-wta-markub-monbar-2026-08-05).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -7051,32 +7071,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>Kayla Cross</t>
+          <t>Mona Barthel</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>Ann Li</t>
+          <t>Martyna Kubka</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -7129,7 +7149,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.491214Z</t>
+          <t>2026-08-05T10:19:06.246493Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7139,19 +7159,23 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-285</v>
+        <v>156</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.350877</v>
+        <v>2.56</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.74026</v>
+        <v>0.390625</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
       <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="28" t="n"/>
+      <c r="BQ20" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR20" s="28" t="n">
+        <v>0.39</v>
+      </c>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
       <c r="BU20" s="25" t="n"/>
@@ -7187,22 +7211,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>f5c109203b344abd</t>
+          <t>41f6571053964a9b</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T10:44:49.997481Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T12:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182208</t>
+          <t>961-2026:182097</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -7212,12 +7236,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -7237,28 +7261,28 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-122</v>
+        <v>-113</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.884956</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.530516</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.646211</v>
+        <v>0.684504</v>
       </c>
       <c r="P21" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.096661</v>
+        <v>0.153988</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7281,7 +7305,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5500 (aec-wta-alikor-emmnav-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5300 (aec-wta-susban-verpod-2026-08-05).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7322,32 +7346,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Veronika Podrez</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Susan Bandecchi</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7400,7 +7424,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:15.073339Z</t>
+          <t>2026-08-05T10:42:35.161195Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7410,13 +7434,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-122</v>
+        <v>-113</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.884956</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.530516</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7458,22 +7482,22 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>aac54ca3098f486d</t>
+          <t>36f2b4a83bab424a</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182214</t>
+          <t>421-2026:182208</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7483,12 +7507,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7508,28 +7532,28 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-178</v>
+        <v>-117</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.854701</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.539171</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.733479</v>
+        <v>0.646211</v>
       </c>
       <c r="P22" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>0.093191</v>
+        <v>0.10704</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
@@ -7552,7 +7576,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.6400 (aec-wta-liusam-barkre-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5400 (aec-wta-alikor-emmnav-2026-08-04).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7593,32 +7617,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7671,7 +7695,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:19.786889Z</t>
+          <t>2026-08-05T13:52:42.200980Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7681,13 +7705,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-178</v>
+        <v>-117</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.854701</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.539171</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7729,22 +7753,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>44bcccd381124b6e</t>
+          <t>2b711e12bdab4d1d</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:30Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182098</t>
+          <t>421-2026:182179</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7754,12 +7778,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7769,7 +7793,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7779,28 +7803,28 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>156</v>
+        <v>-270</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>2.56</v>
+        <v>1.37037</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.72973</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.5849800000000001</v>
+        <v>0.797746</v>
       </c>
       <c r="P23" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q23" s="28" t="n">
-        <v>0.194355</v>
+        <v>0.06801599999999999</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7823,7 +7847,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Mona Barthel p=0.585 vs Martyna Kubka. Executable ask 0.3900 (aec-wta-markub-monbar-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Maya Joint p=0.202 vs Sorana Cirstea. Executable ask 0.7300 (aec-wta-sorcir-mayjoi-2026-08-04).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7864,32 +7888,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>Mona Barthel</t>
+          <t>Maya Joint</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>Martyna Kubka</t>
+          <t>Sorana Cirstea</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7942,7 +7966,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.279442Z</t>
+          <t>2026-08-05T13:52:46.461127Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7952,13 +7976,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>156</v>
+        <v>-270</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>2.56</v>
+        <v>1.37037</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.72973</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -8000,22 +8024,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>e020edf7cfeb46ad</t>
+          <t>e3446e50fda04f75</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T12:00Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>961-2026:182097</t>
+          <t>421-2026:182214</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -8025,12 +8049,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -8050,25 +8074,25 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.694444</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.684504</v>
+        <v>0.733479</v>
       </c>
       <c r="P24" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>0.165273</v>
+        <v>0.143315</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="S24" s="29" t="n">
         <v>2</v>
@@ -8094,7 +8118,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5200 (aec-wta-susban-verpod-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.5900 (aec-wta-liusam-barkre-2026-08-06).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8135,32 +8159,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Veronika Podrez</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>Susan Bandecchi</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8213,7 +8237,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:10.339946Z</t>
+          <t>2026-08-05T13:52:45.892436Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8223,13 +8247,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.694444</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.590164</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8271,22 +8295,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>8e9660411beb46fe</t>
+          <t>8d670cbce19e4458</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T15:00Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181727</t>
+          <t>421-2026:181752</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8296,12 +8320,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8321,28 +8345,28 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-133</v>
+        <v>104</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.490196</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.629315</v>
+        <v>0.5960220000000001</v>
       </c>
       <c r="P25" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q25" s="28" t="n">
-        <v>0.0585</v>
+        <v>0.105826</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8365,7 +8389,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Joao Fonseca p=0.629 vs Stefanos Tsitsipas. Executable ask 0.5700 (aec-atp-stetsi-joafon-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.4900 (aec-atp-miokec-artrin-2026-08-05).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8406,32 +8430,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Stefanos Tsitsipas</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8484,7 +8508,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:29.605345Z</t>
+          <t>2026-08-05T13:52:54.747914Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8494,13 +8518,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-133</v>
+        <v>104</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.490196</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8542,12 +8566,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>d2ae439197534b67</t>
+          <t>a8318311332241c5</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -8557,7 +8581,7 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181752</t>
+          <t>421-2026:181765</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8567,12 +8591,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8592,28 +8616,28 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2</v>
+        <v>1.333333</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.5960220000000001</v>
+        <v>0.814392</v>
       </c>
       <c r="P26" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>0.096022</v>
+        <v>0.064392</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8636,7 +8660,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.5000 (aec-atp-miokec-artrin-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Ben Shelton p=0.814 vs Jenson Brooksby. Executable ask 0.7500 (aec-atp-jenbro-benshe-2026-08-06).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8677,32 +8701,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8755,7 +8779,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:30.228623Z</t>
+          <t>2026-08-05T13:52:57.128543Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8765,13 +8789,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2</v>
+        <v>1.333333</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8813,12 +8837,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>f276d6d0260c4f9f</t>
+          <t>e5b6f93ebaa24dbe</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8863,13 +8887,13 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.4</v>
+        <v>0.420168</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.584869</v>
@@ -8878,7 +8902,7 @@
         <v>0.05</v>
       </c>
       <c r="Q27" s="28" t="n">
-        <v>0.184869</v>
+        <v>0.164701</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>100</v>
@@ -8907,7 +8931,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4000 (aec-atp-hubhur-aletab-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4200 (aec-atp-hubhur-aletab-2026-08-06).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -9026,7 +9050,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:34.393571Z</t>
+          <t>2026-08-05T13:53:00.150232Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9036,13 +9060,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.4</v>
+        <v>0.420168</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -9084,12 +9108,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>21b78587ba4444b3</t>
+          <t>e000b90e638e45ff</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -9297,7 +9321,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:39.206890Z</t>
+          <t>2026-08-05T13:53:01.869933Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9355,22 +9379,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>8c4a1a66a49943db</t>
+          <t>b6f2766f15c84a45</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:19.625619Z</t>
+          <t>2026-08-05T13:54:48.712587Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181733</t>
+          <t>421-2026:181719</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9380,12 +9404,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9395,7 +9419,7 @@
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -9405,25 +9429,25 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-270</v>
+        <v>-223</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.44843</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.690402</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.8122509999999999</v>
+        <v>0.742792</v>
       </c>
       <c r="P29" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q29" s="28" t="n">
-        <v>0.082521</v>
+        <v>0.05239</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>2</v>
@@ -9449,7 +9473,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Botic Van De Zandschulp p=0.188 vs Daniil Medvedev. Executable ask 0.7300 (aec-atp-danmed-botzan-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Jakub Mensik p=0.743 vs Jacob Fearnley. Executable ask 0.6900 (aec-atp-jacfea-jakmen-2026-08-05).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9490,32 +9514,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Jacob Fearnley</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9568,7 +9592,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:34:42.085885Z</t>
+          <t>2026-08-05T13:53:03.385419Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9578,13 +9602,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>-270</v>
+        <v>-223</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.44843</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.690402</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9623,6 +9647,277 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>c2eb15dc90434e89</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:54:48.712587Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T22:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181733</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.8122509999999999</v>
+      </c>
+      <c r="P30" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q30" s="28" t="n">
+        <v>0.062251</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Botic Van De Zandschulp p=0.188 vs Daniil Medvedev. Executable ask 0.7500 (aec-atp-danmed-botzan-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Botic Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:53:04.877388Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS30" headerRowCount="1">
-  <autoFilter ref="A1:CS30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS31" headerRowCount="1">
+  <autoFilter ref="A1:CS31"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$30)</f>
+        <f>COUNTA('Picks'!$A$2:$A$31)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$30,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$30,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")/(COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"win")+COUNTIFS('Picks'!$BX$2:$BX$30,"&gt;0",'Picks'!$V$2:$V$30,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$30)/SUM('Picks'!$BX$2:$BX$30),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$30)</f>
+        <f>SUM('Picks'!$BY$2:$BY$31)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$30,"&lt;&gt;",'Picks'!$AB$2:$AB$30),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$30,'Picks'!$AM$2:$AM$30,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A14,'Picks'!$U$2:$U$30,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A15,'Picks'!$U$2:$U$30,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled",'Picks'!$V$2:$V$30,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$30,'Picks'!$H$2:$H$30,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$30,'Picks'!$H$2:$H$30,$A16,'Picks'!$U$2:$U$30,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS30"/>
+  <dimension ref="A1:CS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7291,18 +7291,38 @@
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="28" t="n"/>
-      <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="Z21" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA21" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB21" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC21" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:59:37.870671Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Veronika Podrez p=0.685 vs Susan Bandecchi. Executable ask 0.5300 (aec-wta-susban-verpod-2026-08-05).</t>
@@ -7315,7 +7335,7 @@
       </c>
       <c r="AG21" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH21" s="24" t="n"/>
@@ -7445,8 +7465,12 @@
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
       <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
-      <c r="BR21" s="28" t="n"/>
+      <c r="BQ21" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR21" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
       <c r="BU21" s="25" t="n"/>
@@ -7482,7 +7506,7 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>36f2b4a83bab424a</t>
+          <t>8d670cbce19e4458</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
@@ -7492,12 +7516,12 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182208</t>
+          <t>421-2026:181752</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7507,12 +7531,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7532,28 +7556,28 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.04</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.490196</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.646211</v>
+        <v>0.5960220000000001</v>
       </c>
       <c r="P22" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>0.10704</v>
+        <v>0.105826</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
@@ -7562,21 +7586,41 @@
       </c>
       <c r="U22" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="28" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
+      <c r="Z22" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA22" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB22" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC22" s="30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:58.514616Z</t>
+        </is>
+      </c>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5400 (aec-wta-alikor-emmnav-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.4900 (aec-atp-miokec-artrin-2026-08-05).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7617,32 +7661,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>Emma Navarro</t>
+          <t>Arthur Rinderknech</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>Alina Korneeva</t>
+          <t>Miomir Kecmanovic</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7695,7 +7739,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:42.200980Z</t>
+          <t>2026-08-05T13:52:54.747914Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7705,19 +7749,23 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.04</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.490196</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
       <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
-      <c r="BR22" s="28" t="n"/>
+      <c r="BQ22" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR22" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
       <c r="BU22" s="25" t="n"/>
@@ -7753,7 +7801,7 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>2b711e12bdab4d1d</t>
+          <t>a8318311332241c5</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
@@ -7763,12 +7811,12 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T16:30Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182179</t>
+          <t>421-2026:181765</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7778,12 +7826,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7793,7 +7841,7 @@
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J23" s="25" t="n"/>
@@ -7803,25 +7851,25 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-270</v>
+        <v>-300</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.333333</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.75</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.797746</v>
+        <v>0.814392</v>
       </c>
       <c r="P23" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q23" s="28" t="n">
-        <v>0.06801599999999999</v>
+        <v>0.064392</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>2</v>
@@ -7833,21 +7881,41 @@
       </c>
       <c r="U23" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V23" s="24" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y23" s="25" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="28" t="n"/>
-      <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n"/>
-      <c r="AD23" s="24" t="n"/>
+      <c r="Z23" s="26" t="n">
+        <v>-300</v>
+      </c>
+      <c r="AA23" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB23" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:58.775278Z</t>
+        </is>
+      </c>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Maya Joint p=0.202 vs Sorana Cirstea. Executable ask 0.7300 (aec-wta-sorcir-mayjoi-2026-08-04).</t>
+          <t>Surface-blended Elo on Hard: Ben Shelton p=0.814 vs Jenson Brooksby. Executable ask 0.7500 (aec-atp-jenbro-benshe-2026-08-06).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7888,32 +7956,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>Maya Joint</t>
+          <t>Ben Shelton</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>Sorana Cirstea</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7966,7 +8034,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:46.461127Z</t>
+          <t>2026-08-05T13:52:57.128543Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7976,19 +8044,23 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-270</v>
+        <v>-300</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.333333</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.75</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
       <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
-      <c r="BR23" s="28" t="n"/>
+      <c r="BQ23" s="27" t="n">
+        <v>1.333333</v>
+      </c>
+      <c r="BR23" s="28" t="n">
+        <v>0.75</v>
+      </c>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
       <c r="BU23" s="25" t="n"/>
@@ -8024,22 +8096,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>e3446e50fda04f75</t>
+          <t>90629adc75584dc7</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-05T17:03:22.897552Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>421-2026:182214</t>
+          <t>421-2026:182208</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -8049,12 +8121,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -8074,28 +8146,28 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-144</v>
+        <v>-113</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.884956</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.530516</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.733479</v>
+        <v>0.646211</v>
       </c>
       <c r="P24" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>0.143315</v>
+        <v>0.115695</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -8104,21 +8176,41 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:58.996785Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.5900 (aec-wta-liusam-barkre-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Emma Navarro p=0.646 vs Alina Korneeva. Executable ask 0.5300 (aec-wta-alikor-emmnav-2026-08-04).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -8128,7 +8220,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -8159,32 +8251,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Barbora Krejcikova</t>
+          <t>Emma Navarro</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>Liudmila Samsonova</t>
+          <t>Alina Korneeva</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8237,7 +8329,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:45.892436Z</t>
+          <t>2026-08-05T17:01:59.688625Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8247,19 +8339,23 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-144</v>
+        <v>-113</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.694444</v>
+        <v>1.884956</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.530516</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
@@ -8295,22 +8391,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>8d670cbce19e4458</t>
+          <t>09599bf5cbe04156</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-05T17:03:22.897552Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T21:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181752</t>
+          <t>421-2026:182214</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8320,12 +8416,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8345,28 +8441,28 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>104</v>
+        <v>-144</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>2.04</v>
+        <v>1.694444</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.590164</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.5960220000000001</v>
+        <v>0.733479</v>
       </c>
       <c r="P25" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q25" s="28" t="n">
-        <v>0.105826</v>
+        <v>0.143315</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8375,21 +8471,41 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:17.500696Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Arthur Rinderknech p=0.596 vs Miomir Kecmanovic. Executable ask 0.4900 (aec-atp-miokec-artrin-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Barbora Krejcikova p=0.733 vs Liudmila Samsonova. Executable ask 0.5900 (aec-wta-liusam-barkre-2026-08-06).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8399,7 +8515,7 @@
       </c>
       <c r="AG25" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH25" s="24" t="n"/>
@@ -8430,32 +8546,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>Arthur Rinderknech</t>
+          <t>Barbora Krejcikova</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Miomir Kecmanovic</t>
+          <t>Liudmila Samsonova</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8508,7 +8624,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:54.747914Z</t>
+          <t>2026-08-05T17:02:04.621209Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8518,19 +8634,23 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>104</v>
+        <v>-144</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>2.04</v>
+        <v>1.694444</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.590164</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
@@ -8566,22 +8686,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>a8318311332241c5</t>
+          <t>4eafd76864b640e2</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-05T17:03:22.897552Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T16:30Z</t>
+          <t>2026-08-05T18:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181765</t>
+          <t>421-2026:181743</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8591,12 +8711,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8616,28 +8736,28 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-300</v>
+        <v>138</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.333333</v>
+        <v>2.38</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.75</v>
+        <v>0.420168</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.814392</v>
+        <v>0.584869</v>
       </c>
       <c r="P26" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>0.064392</v>
+        <v>0.164701</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8646,21 +8766,41 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T20:57:59.221074Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Ben Shelton p=0.814 vs Jenson Brooksby. Executable ask 0.7500 (aec-atp-jenbro-benshe-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4200 (aec-atp-hubhur-aletab-2026-08-06).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8670,7 +8810,7 @@
       </c>
       <c r="AG26" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH26" s="24" t="n"/>
@@ -8701,32 +8841,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Ben Shelton</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Hubert Hurkacz</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8779,7 +8919,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:57.128543Z</t>
+          <t>2026-08-05T17:02:15.869129Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8789,19 +8929,23 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-300</v>
+        <v>138</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.333333</v>
+        <v>2.38</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.75</v>
+        <v>0.420168</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.42</v>
+      </c>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
       <c r="BU26" s="25" t="n"/>
@@ -8837,22 +8981,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>e5b6f93ebaa24dbe</t>
+          <t>a32e4b4ca87943a1</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-05T17:03:22.897552Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:00Z</t>
+          <t>2026-08-05T19:30Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181743</t>
+          <t>421-2026:181753</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8862,12 +9006,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8887,28 +9031,28 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.584869</v>
+        <v>0.657899</v>
       </c>
       <c r="P27" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q27" s="28" t="n">
-        <v>0.164701</v>
+        <v>0.248063</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -8917,21 +9061,41 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:20:17.768639Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Alejandro Tabilo p=0.585 vs Hubert Hurkacz. Executable ask 0.4200 (aec-atp-hubhur-aletab-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Francisco Cerundolo p=0.658 vs Alex Michelsen. Executable ask 0.4100 (aec-atp-alemic-fracer-2026-08-06).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8941,7 +9105,7 @@
       </c>
       <c r="AG27" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH27" s="24" t="n"/>
@@ -8972,32 +9136,32 @@
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Tabilo</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Alex Michelsen</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -9050,7 +9214,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:53:00.150232Z</t>
+          <t>2026-08-05T17:02:18.609359Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9060,19 +9224,23 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.41</v>
+      </c>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
       <c r="BU27" s="25" t="n"/>
@@ -9108,22 +9276,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>e000b90e638e45ff</t>
+          <t>cbce5a7195d54c42</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-06T18:58:42.068094Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:30Z</t>
+          <t>2026-08-06T21:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181753</t>
+          <t>421-2026:182193</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -9133,12 +9301,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -9158,28 +9326,28 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>150</v>
+        <v>-194</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.5</v>
+        <v>1.515464</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.4</v>
+        <v>0.659864</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.657899</v>
+        <v>0.7591</v>
       </c>
       <c r="P28" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q28" s="28" t="n">
-        <v>0.257899</v>
+        <v>0.099236</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -9188,21 +9356,41 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28" t="n"/>
-      <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:22.233516Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Francisco Cerundolo p=0.658 vs Alex Michelsen. Executable ask 0.4000 (aec-atp-alemic-fracer-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Amanda Anisimova p=0.759 vs Nikola Bartunkova. Executable ask 0.6600 (aec-wta-nikbar-amaani-2026-08-06).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9243,32 +9431,32 @@
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>Francisco Cerundolo</t>
+          <t>Amanda Anisimova</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>Alex Michelsen</t>
+          <t>Nikola Bartunkova</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -9321,7 +9509,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:53:01.869933Z</t>
+          <t>2026-08-06T18:58:03.210799Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9331,19 +9519,23 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>150</v>
+        <v>-194</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.5</v>
+        <v>1.515464</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.4</v>
+        <v>0.659864</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
       <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
-      <c r="BR28" s="28" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.66</v>
+      </c>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
       <c r="BU28" s="25" t="n"/>
@@ -9379,22 +9571,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>b6f2766f15c84a45</t>
+          <t>854a414968094de3</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-06T18:58:42.068094Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T21:00Z</t>
+          <t>2026-08-06T23:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181719</t>
+          <t>421-2026:181763</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9404,12 +9596,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9429,28 +9621,28 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-223</v>
+        <v>127</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.27</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.440529</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.742792</v>
+        <v>0.544019</v>
       </c>
       <c r="P29" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q29" s="28" t="n">
-        <v>0.05239</v>
+        <v>0.10349</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9459,21 +9651,41 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
-      <c r="Z29" s="26" t="n"/>
-      <c r="AA29" s="28" t="n"/>
-      <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="Z29" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA29" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB29" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC29" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:06:22.512232Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Jakub Mensik p=0.743 vs Jacob Fearnley. Executable ask 0.6900 (aec-atp-jacfea-jakmen-2026-08-05).</t>
+          <t>Surface-blended Elo on Hard: Lorenzo Musetti p=0.544 vs Rafael Jodar. Executable ask 0.4400 (aec-atp-rafjod-lormus-2026-08-06).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9483,7 +9695,7 @@
       </c>
       <c r="AG29" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH29" s="24" t="n"/>
@@ -9514,32 +9726,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>Jakub Mensik</t>
+          <t>Lorenzo Musetti</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Jacob Fearnley</t>
+          <t>Rafael Jodar</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9592,7 +9804,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:53:03.385419Z</t>
+          <t>2026-08-06T18:58:10.033097Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9602,19 +9814,23 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>-223</v>
+        <v>127</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.27</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.440529</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
       <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
-      <c r="BR29" s="28" t="n"/>
+      <c r="BQ29" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR29" s="28" t="n">
+        <v>0.44</v>
+      </c>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
       <c r="BU29" s="25" t="n"/>
@@ -9650,22 +9866,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>c2eb15dc90434e89</t>
+          <t>56254b0ff65c48f8</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:48.712587Z</t>
+          <t>2026-08-07T09:10:09.393141Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T22:00Z</t>
+          <t>2026-08-07T10:00Z</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>421-2026:181733</t>
+          <t>961-2026:182110</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9675,12 +9891,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9690,7 +9906,7 @@
       </c>
       <c r="I30" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J30" s="25" t="n"/>
@@ -9700,28 +9916,28 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-300</v>
+        <v>138</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.333333</v>
+        <v>2.38</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.75</v>
+        <v>0.420168</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.8122509999999999</v>
+        <v>0.551853</v>
       </c>
       <c r="P30" s="28" t="n">
         <v>0.05</v>
       </c>
       <c r="Q30" s="28" t="n">
-        <v>0.062251</v>
+        <v>0.131685</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9730,21 +9946,41 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28" t="n"/>
-      <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="Z30" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:12:32.744915Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Surface-blended Elo on Hard: Botic Van De Zandschulp p=0.188 vs Daniil Medvedev. Executable ask 0.7500 (aec-atp-danmed-botzan-2026-08-06).</t>
+          <t>Surface-blended Elo on Hard: Gabriela Knutson p=0.552 vs Elizara Yaneva. Executable ask 0.4200 (aec-wta-eliyan-gabknu-2026-08-07).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9785,32 +10021,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>Botic Van De Zandschulp</t>
+          <t>Gabriela Knutson</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>Daniil Medvedev</t>
+          <t>Elizara Yaneva</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9863,7 +10099,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:53:04.877388Z</t>
+          <t>2026-08-07T09:08:50.003635Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9873,19 +10109,23 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>-300</v>
+        <v>138</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.333333</v>
+        <v>2.38</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.75</v>
+        <v>0.420168</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
       <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
-      <c r="BR30" s="28" t="n"/>
+      <c r="BQ30" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR30" s="28" t="n">
+        <v>0.42</v>
+      </c>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
       <c r="BU30" s="25" t="n"/>
@@ -9918,6 +10158,277 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>563e585b216b4f2f</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:22:21.644116Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T23:30Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>421-2026:181766</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.592411</v>
+      </c>
+      <c r="P31" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q31" s="28" t="n">
+        <v>0.131582</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Thiago Agustin Tirante p=0.592 vs Alexei Popyrin. Executable ask 0.4600 (aec-atp-alepop-thitir-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:55.272443Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -10161,12 +10161,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>563e585b216b4f2f</t>
+          <t>12c791275d1d4803</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:21.644116Z</t>
+          <t>2026-08-07T18:29:30.567007Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:55.272443Z</t>
+          <t>2026-08-07T18:28:15.652471Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">

--- a/data/main/tennis.xlsx
+++ b/data/main/tennis.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
-  <autoFilter ref="A1:CS38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS39" headerRowCount="1">
+  <autoFilter ref="A1:CS39"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$38)</f>
+        <f>COUNTA('Picks'!$A$2:$A$39)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$38)</f>
+        <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS38"/>
+  <dimension ref="A1:CS39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12011,18 +12011,38 @@
       </c>
       <c r="U37" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="26" t="n"/>
-      <c r="AA37" s="28" t="n"/>
-      <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
+      <c r="Z37" s="26" t="n">
+        <v>-245</v>
+      </c>
+      <c r="AA37" s="28" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB37" s="28" t="n">
+        <v>-0.000145</v>
+      </c>
+      <c r="AC37" s="30" t="n">
+        <v>0.8163</v>
+      </c>
+      <c r="AD37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:13:46.977830Z</t>
+        </is>
+      </c>
       <c r="AE37" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Elina Svitolina p=0.765 vs Ekaterina Alexandrova. Executable ask 0.7100 (aec-wta-ekaale-elisvi-2026-08-11).</t>
@@ -12165,8 +12185,12 @@
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
       <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
-      <c r="BR37" s="28" t="n"/>
+      <c r="BQ37" s="27" t="n">
+        <v>1.408163</v>
+      </c>
+      <c r="BR37" s="28" t="n">
+        <v>0.71</v>
+      </c>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
       <c r="BU37" s="25" t="n"/>
@@ -12282,18 +12306,38 @@
       </c>
       <c r="U38" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
+      <c r="Z38" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA38" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB38" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC38" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:13:47.249123Z</t>
+        </is>
+      </c>
       <c r="AE38" s="31" t="inlineStr">
         <is>
           <t>Surface-blended Elo on Hard: Arthur Fils p=0.609 vs Rafael Jodar. Executable ask 0.4600 (aec-atp-rafjod-artfil-2026-08-11).</t>
@@ -12306,7 +12350,7 @@
       </c>
       <c r="AG38" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH38" s="24" t="n"/>
@@ -12436,8 +12480,12 @@
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
       <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
-      <c r="BR38" s="28" t="n"/>
+      <c r="BQ38" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR38" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
       <c r="BU38" s="25" t="n"/>
@@ -12470,6 +12518,277 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>5f2a09f640414434</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:45:46.281726Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>718-2026:184475</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>TENNIS</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.57778</v>
+      </c>
+      <c r="P39" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q39" s="28" t="n">
+        <v>0.17778</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo on Hard: Polina Kudermetova p=0.578 vs Wang Xiyu. Executable ask 0.4000 (aec-wta-xiywan-polkud-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Surface-blended Elo model; singles only, WTA+ATP market coverage, not yet locked-holdout qualified -- promoted by explicit operator directive, not genuine walk-forward validation.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Polina Kudermetova</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>Wang Xiyu</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>surface_blended_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:36.206620Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
